--- a/data/cases-de.xlsx
+++ b/data/cases-de.xlsx
@@ -1,87 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/torben/Hacken/GitHub/COVID-19-Coronavirus-German-Regions/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49665D7F-AC9C-4A49-99CE-ACA9B0829AED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14300" activeTab="6" xr2:uid="{309167EE-B9E7-9F44-B3F3-07C1908B9528}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Links" sheetId="10" r:id="rId1"/>
-    <sheet name="Input" sheetId="4" r:id="rId2"/>
-    <sheet name="AllDays" sheetId="6" r:id="rId3"/>
-    <sheet name="AllDaysTranposed" sheetId="7" r:id="rId4"/>
-    <sheet name="Cases" sheetId="8" r:id="rId5"/>
-    <sheet name="Cases Change" sheetId="11" r:id="rId6"/>
-    <sheet name="Cases Rel" sheetId="14" r:id="rId7"/>
-    <sheet name="Death" sheetId="5" r:id="rId8"/>
-    <sheet name="RefPopulation" sheetId="12" r:id="rId9"/>
-    <sheet name="When will it be 1 Mill cases" sheetId="13" r:id="rId10"/>
-  </sheets>
-  <definedNames>
-    <definedName name="date_last_DE_Total">'Cases Rel'!$C$3</definedName>
-    <definedName name="guide_doubling">Cases!$Z$4</definedName>
-    <definedName name="guide_start">Cases!$Z$3</definedName>
-    <definedName name="laast_BY">'Cases Rel'!$C$6</definedName>
-    <definedName name="last_BB">'Cases Rel'!$C$8</definedName>
-    <definedName name="last_BE">'Cases Rel'!$C$7</definedName>
-    <definedName name="last_BW">'Cases Rel'!$C$5</definedName>
-    <definedName name="last_BY">'Cases Rel'!$C$6</definedName>
-    <definedName name="last_DE_Total">'Cases Rel'!$C$21</definedName>
-    <definedName name="last_HB">'Cases Rel'!$C$9</definedName>
-    <definedName name="last_HE">'Cases Rel'!$C$11</definedName>
-    <definedName name="last_HH">'Cases Rel'!$C$10</definedName>
-    <definedName name="last_MV">'Cases Rel'!$C$12</definedName>
-    <definedName name="last_NI">'Cases Rel'!$C$13</definedName>
-    <definedName name="last_NW">'Cases Rel'!$C$14</definedName>
-    <definedName name="last_RP">'Cases Rel'!$C$15</definedName>
-    <definedName name="last_SA">'Cases Rel'!$C$18</definedName>
-    <definedName name="last_SH">'Cases Rel'!$C$19</definedName>
-    <definedName name="last_SL">'Cases Rel'!$C$16</definedName>
-    <definedName name="last_SN">'Cases Rel'!$C$17</definedName>
-    <definedName name="last_ST">'Cases Rel'!$C$18</definedName>
-    <definedName name="last_TH">'Cases Rel'!$C$20</definedName>
-    <definedName name="min_number">'Cases Change'!$U$2</definedName>
-    <definedName name="per_pop_scale">'Cases Rel'!$D$2</definedName>
-    <definedName name="pop_BB">RefPopulation!$C$7</definedName>
-    <definedName name="pop_BE">RefPopulation!$C$6</definedName>
-    <definedName name="pop_BW">RefPopulation!$C$4</definedName>
-    <definedName name="pop_BY">RefPopulation!$C$5</definedName>
-    <definedName name="pop_DE_Total">RefPopulation!$C$20</definedName>
-    <definedName name="pop_HB">RefPopulation!$C$8</definedName>
-    <definedName name="pop_HE">RefPopulation!$C$10</definedName>
-    <definedName name="pop_HH">RefPopulation!$C$9</definedName>
-    <definedName name="pop_MV">RefPopulation!$C$11</definedName>
-    <definedName name="pop_NI">RefPopulation!$C$12</definedName>
-    <definedName name="pop_NW">RefPopulation!$C$13</definedName>
-    <definedName name="pop_RP">RefPopulation!$C$14</definedName>
-    <definedName name="pop_SA">RefPopulation!$C$17</definedName>
-    <definedName name="pop_SH">RefPopulation!$C$18</definedName>
-    <definedName name="pop_SL">RefPopulation!$C$15</definedName>
-    <definedName name="pop_SN">RefPopulation!$C$16</definedName>
-    <definedName name="pop_ST">RefPopulation!$C$17</definedName>
-    <definedName name="pop_TH">RefPopulation!$C$19</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
@@ -12950,4289 +12866,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F5B1F18-8A79-3242-815B-7FAFD236451B}">
-  <dimension ref="A1:T51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="2" max="2" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="8.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" s="8" customFormat="1" ht="142">
-      <c r="A1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="49">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>43889.416666666664</v>
-      </c>
-      <c r="C2" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="79">
-        <v>10</v>
-      </c>
-      <c r="E2" s="79">
-        <v>15</v>
-      </c>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79">
-        <v>25</v>
-      </c>
-      <c r="N2" s="79">
-        <v>2</v>
-      </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79">
-        <v>1</v>
-      </c>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="49">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>43890.416666666664</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="80">
-        <v>14</v>
-      </c>
-      <c r="E3" s="80">
-        <v>15</v>
-      </c>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80">
-        <v>3</v>
-      </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80">
-        <v>30</v>
-      </c>
-      <c r="N3" s="80">
-        <v>1</v>
-      </c>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80">
-        <v>1</v>
-      </c>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="49">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
-        <v>43891.625</v>
-      </c>
-      <c r="C4" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="79">
-        <v>15</v>
-      </c>
-      <c r="E4" s="79">
-        <v>23</v>
-      </c>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79">
-        <v>1</v>
-      </c>
-      <c r="I4" s="79">
-        <v>1</v>
-      </c>
-      <c r="J4" s="79">
-        <v>8</v>
-      </c>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79">
-        <v>1</v>
-      </c>
-      <c r="M4" s="79">
-        <v>74</v>
-      </c>
-      <c r="N4" s="79">
-        <v>2</v>
-      </c>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79">
-        <v>2</v>
-      </c>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" s="49">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>43892.625</v>
-      </c>
-      <c r="C5" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="80">
-        <v>20</v>
-      </c>
-      <c r="E5" s="80">
-        <v>26</v>
-      </c>
-      <c r="F5" s="80">
-        <v>1</v>
-      </c>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80">
-        <v>1</v>
-      </c>
-      <c r="I5" s="80">
-        <v>2</v>
-      </c>
-      <c r="J5" s="80">
-        <v>10</v>
-      </c>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80">
-        <v>1</v>
-      </c>
-      <c r="M5" s="80">
-        <v>90</v>
-      </c>
-      <c r="N5" s="80">
-        <v>2</v>
-      </c>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80">
-        <v>2</v>
-      </c>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="49">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>43893.625</v>
-      </c>
-      <c r="C6" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="79">
-        <v>28</v>
-      </c>
-      <c r="E6" s="79">
-        <v>37</v>
-      </c>
-      <c r="F6" s="79">
-        <v>3</v>
-      </c>
-      <c r="G6" s="79">
-        <v>1</v>
-      </c>
-      <c r="H6" s="79">
-        <v>2</v>
-      </c>
-      <c r="I6" s="79">
-        <v>2</v>
-      </c>
-      <c r="J6" s="79">
-        <v>12</v>
-      </c>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79">
-        <v>2</v>
-      </c>
-      <c r="M6" s="79">
-        <v>103</v>
-      </c>
-      <c r="N6" s="79">
-        <v>2</v>
-      </c>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79">
-        <v>2</v>
-      </c>
-      <c r="S6" s="79">
-        <v>1</v>
-      </c>
-      <c r="T6" s="79">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="49">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4">
-        <v>43894.625</v>
-      </c>
-      <c r="C7" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="80">
-        <v>50</v>
-      </c>
-      <c r="E7" s="80">
-        <v>48</v>
-      </c>
-      <c r="F7" s="80">
-        <v>7</v>
-      </c>
-      <c r="G7" s="80">
-        <v>1</v>
-      </c>
-      <c r="H7" s="80">
-        <v>3</v>
-      </c>
-      <c r="I7" s="80">
-        <v>3</v>
-      </c>
-      <c r="J7" s="80">
-        <v>12</v>
-      </c>
-      <c r="K7" s="80">
-        <v>4</v>
-      </c>
-      <c r="L7" s="80">
-        <v>7</v>
-      </c>
-      <c r="M7" s="80">
-        <v>115</v>
-      </c>
-      <c r="N7" s="80">
-        <v>7</v>
-      </c>
-      <c r="O7" s="80">
-        <v>1</v>
-      </c>
-      <c r="P7" s="80">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="80"/>
-      <c r="R7" s="80">
-        <v>2</v>
-      </c>
-      <c r="S7" s="80">
-        <v>1</v>
-      </c>
-      <c r="T7" s="80">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="49">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4">
-        <v>43895.625</v>
-      </c>
-      <c r="C8" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="79">
-        <v>73</v>
-      </c>
-      <c r="E8" s="79">
-        <v>70</v>
-      </c>
-      <c r="F8" s="79">
-        <v>13</v>
-      </c>
-      <c r="G8" s="79">
-        <v>1</v>
-      </c>
-      <c r="H8" s="79">
-        <v>3</v>
-      </c>
-      <c r="I8" s="79">
-        <v>5</v>
-      </c>
-      <c r="J8" s="79">
-        <v>14</v>
-      </c>
-      <c r="K8" s="79">
-        <v>4</v>
-      </c>
-      <c r="L8" s="79">
-        <v>18</v>
-      </c>
-      <c r="M8" s="79">
-        <v>181</v>
-      </c>
-      <c r="N8" s="79">
-        <v>8</v>
-      </c>
-      <c r="O8" s="79">
-        <v>1</v>
-      </c>
-      <c r="P8" s="79">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="79"/>
-      <c r="R8" s="79">
-        <v>7</v>
-      </c>
-      <c r="S8" s="79">
-        <v>1</v>
-      </c>
-      <c r="T8" s="79">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="49">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4">
-        <v>43896.625</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="66">
-        <v>96</v>
-      </c>
-      <c r="E9" s="66">
-        <v>117</v>
-      </c>
-      <c r="F9" s="66">
-        <v>19</v>
-      </c>
-      <c r="G9" s="66">
-        <v>2</v>
-      </c>
-      <c r="H9" s="66">
-        <v>4</v>
-      </c>
-      <c r="I9" s="66">
-        <v>11</v>
-      </c>
-      <c r="J9" s="66">
-        <v>16</v>
-      </c>
-      <c r="K9" s="66">
-        <v>5</v>
-      </c>
-      <c r="L9" s="66">
-        <v>18</v>
-      </c>
-      <c r="M9" s="66">
-        <v>329</v>
-      </c>
-      <c r="N9" s="66">
-        <v>10</v>
-      </c>
-      <c r="O9" s="66">
-        <v>2</v>
-      </c>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66">
-        <v>2</v>
-      </c>
-      <c r="R9" s="66">
-        <v>7</v>
-      </c>
-      <c r="S9" s="66">
-        <v>1</v>
-      </c>
-      <c r="T9" s="66">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="49">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4">
-        <v>43896.625</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79">
-        <v>1</v>
-      </c>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="79"/>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="49">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4">
-        <v>43897.625</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="80">
-        <v>170</v>
-      </c>
-      <c r="E11" s="80">
-        <v>134</v>
-      </c>
-      <c r="F11" s="80">
-        <v>28</v>
-      </c>
-      <c r="G11" s="80">
-        <v>2</v>
-      </c>
-      <c r="H11" s="80">
-        <v>4</v>
-      </c>
-      <c r="I11" s="80">
-        <v>13</v>
-      </c>
-      <c r="J11" s="80">
-        <v>17</v>
-      </c>
-      <c r="K11" s="80">
-        <v>5</v>
-      </c>
-      <c r="L11" s="80">
-        <v>19</v>
-      </c>
-      <c r="M11" s="80">
-        <v>373</v>
-      </c>
-      <c r="N11" s="80">
-        <v>13</v>
-      </c>
-      <c r="O11" s="80">
-        <v>3</v>
-      </c>
-      <c r="P11" s="80">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80">
-        <v>8</v>
-      </c>
-      <c r="S11" s="80">
-        <v>2</v>
-      </c>
-      <c r="T11" s="80">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="49">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4">
-        <v>43897.625</v>
-      </c>
-      <c r="C12" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79">
-        <v>1</v>
-      </c>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="79"/>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="49">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4">
-        <v>43898.625</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="80">
-        <v>182</v>
-      </c>
-      <c r="E13" s="80">
-        <v>172</v>
-      </c>
-      <c r="F13" s="80">
-        <v>40</v>
-      </c>
-      <c r="G13" s="80">
-        <v>4</v>
-      </c>
-      <c r="H13" s="80">
-        <v>4</v>
-      </c>
-      <c r="I13" s="80">
-        <v>13</v>
-      </c>
-      <c r="J13" s="80">
-        <v>19</v>
-      </c>
-      <c r="K13" s="80">
-        <v>8</v>
-      </c>
-      <c r="L13" s="80">
-        <v>21</v>
-      </c>
-      <c r="M13" s="80">
-        <v>398</v>
-      </c>
-      <c r="N13" s="80">
-        <v>19</v>
-      </c>
-      <c r="O13" s="80">
-        <v>4</v>
-      </c>
-      <c r="P13" s="80">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="80"/>
-      <c r="R13" s="80">
-        <v>9</v>
-      </c>
-      <c r="S13" s="80">
-        <v>2</v>
-      </c>
-      <c r="T13" s="80">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="49">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>43898.625</v>
-      </c>
-      <c r="C14" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79">
-        <v>1</v>
-      </c>
-      <c r="N14" s="79"/>
-      <c r="O14" s="79"/>
-      <c r="P14" s="79"/>
-      <c r="Q14" s="79"/>
-      <c r="R14" s="79"/>
-      <c r="S14" s="79"/>
-      <c r="T14" s="79"/>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="49">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4">
-        <v>43899.625</v>
-      </c>
-      <c r="C15" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="80">
-        <v>204</v>
-      </c>
-      <c r="E15" s="80">
-        <v>256</v>
-      </c>
-      <c r="F15" s="80">
-        <v>48</v>
-      </c>
-      <c r="G15" s="80">
-        <v>6</v>
-      </c>
-      <c r="H15" s="80">
-        <v>4</v>
-      </c>
-      <c r="I15" s="80">
-        <v>17</v>
-      </c>
-      <c r="J15" s="80">
-        <v>26</v>
-      </c>
-      <c r="K15" s="80">
-        <v>10</v>
-      </c>
-      <c r="L15" s="80">
-        <v>38</v>
-      </c>
-      <c r="M15" s="80">
-        <v>484</v>
-      </c>
-      <c r="N15" s="80">
-        <v>17</v>
-      </c>
-      <c r="O15" s="80">
-        <v>6</v>
-      </c>
-      <c r="P15" s="80">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80">
-        <v>9</v>
-      </c>
-      <c r="S15" s="80">
-        <v>2</v>
-      </c>
-      <c r="T15" s="80">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="49">
-        <v>10</v>
-      </c>
-      <c r="B16" s="4">
-        <v>43899.625</v>
-      </c>
-      <c r="C16" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79">
-        <v>2</v>
-      </c>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="49">
-        <v>10</v>
-      </c>
-      <c r="B17" s="4">
-        <v>43899.625</v>
-      </c>
-      <c r="C17" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="80">
-        <v>1</v>
-      </c>
-      <c r="N17" s="80"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="80"/>
-      <c r="S17" s="80"/>
-      <c r="T17" s="80"/>
-    </row>
-    <row r="18" spans="1:20" s="14" customFormat="1">
-      <c r="A18" s="81">
-        <v>11</v>
-      </c>
-      <c r="B18" s="4">
-        <v>43900.625</v>
-      </c>
-      <c r="C18" s="82" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="82">
-        <v>237</v>
-      </c>
-      <c r="E18" s="82">
-        <v>314</v>
-      </c>
-      <c r="F18" s="82">
-        <v>48</v>
-      </c>
-      <c r="G18" s="82">
-        <v>9</v>
-      </c>
-      <c r="H18" s="82">
-        <v>4</v>
-      </c>
-      <c r="I18" s="82">
-        <v>29</v>
-      </c>
-      <c r="J18" s="82">
-        <v>35</v>
-      </c>
-      <c r="K18" s="82">
-        <v>13</v>
-      </c>
-      <c r="L18" s="82">
-        <v>49</v>
-      </c>
-      <c r="M18" s="82">
-        <v>484</v>
-      </c>
-      <c r="N18" s="82">
-        <v>25</v>
-      </c>
-      <c r="O18" s="82">
-        <v>7</v>
-      </c>
-      <c r="P18" s="82">
-        <v>22</v>
-      </c>
-      <c r="Q18" s="82">
-        <v>7</v>
-      </c>
-      <c r="R18" s="82">
-        <v>9</v>
-      </c>
-      <c r="S18" s="82">
-        <v>4</v>
-      </c>
-      <c r="T18" s="81">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="49">
-        <v>11</v>
-      </c>
-      <c r="B19" s="4">
-        <v>43900.625</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80">
-        <v>2</v>
-      </c>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="80"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80">
-        <f>SUM(D19:S19)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="49">
-        <v>11</v>
-      </c>
-      <c r="B20" s="4">
-        <v>43900.625</v>
-      </c>
-      <c r="C20" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79">
-        <v>1</v>
-      </c>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="79"/>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="49">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4">
-        <v>43901.625</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="80">
-        <v>277</v>
-      </c>
-      <c r="E21" s="80">
-        <v>366</v>
-      </c>
-      <c r="F21" s="80">
-        <v>90</v>
-      </c>
-      <c r="G21" s="80">
-        <v>24</v>
-      </c>
-      <c r="H21" s="80">
-        <v>21</v>
-      </c>
-      <c r="I21" s="80">
-        <v>48</v>
-      </c>
-      <c r="J21" s="80">
-        <v>48</v>
-      </c>
-      <c r="K21" s="80">
-        <v>17</v>
-      </c>
-      <c r="L21" s="80">
-        <v>75</v>
-      </c>
-      <c r="M21" s="80">
-        <v>484</v>
-      </c>
-      <c r="N21" s="80">
-        <v>25</v>
-      </c>
-      <c r="O21" s="80">
-        <v>14</v>
-      </c>
-      <c r="P21" s="80">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="80">
-        <v>15</v>
-      </c>
-      <c r="R21" s="80">
-        <v>27</v>
-      </c>
-      <c r="S21" s="80">
-        <v>10</v>
-      </c>
-      <c r="T21" s="80">
-        <v>1567</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="49">
-        <v>12</v>
-      </c>
-      <c r="B22" s="4">
-        <v>43901.625</v>
-      </c>
-      <c r="C22" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="79">
-        <v>3</v>
-      </c>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="79"/>
-      <c r="S22" s="79"/>
-      <c r="T22" s="79">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="49">
-        <v>12</v>
-      </c>
-      <c r="B23" s="4">
-        <v>43901.625</v>
-      </c>
-      <c r="C23" s="83" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83">
-        <v>1</v>
-      </c>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="49">
-        <v>13</v>
-      </c>
-      <c r="B24" s="4">
-        <v>43902.625</v>
-      </c>
-      <c r="C24" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="80">
-        <v>454</v>
-      </c>
-      <c r="E24" s="80">
-        <v>500</v>
-      </c>
-      <c r="F24" s="80">
-        <v>137</v>
-      </c>
-      <c r="G24" s="80">
-        <v>30</v>
-      </c>
-      <c r="H24" s="80">
-        <v>38</v>
-      </c>
-      <c r="I24" s="80">
-        <v>88</v>
-      </c>
-      <c r="J24" s="80">
-        <v>99</v>
-      </c>
-      <c r="K24" s="80">
-        <v>23</v>
-      </c>
-      <c r="L24" s="80">
-        <v>129</v>
-      </c>
-      <c r="M24" s="80">
-        <v>688</v>
-      </c>
-      <c r="N24" s="80">
-        <v>52</v>
-      </c>
-      <c r="O24" s="80">
-        <v>14</v>
-      </c>
-      <c r="P24" s="80">
-        <v>45</v>
-      </c>
-      <c r="Q24" s="80">
-        <v>27</v>
-      </c>
-      <c r="R24" s="80">
-        <v>31</v>
-      </c>
-      <c r="S24" s="80">
-        <v>14</v>
-      </c>
-      <c r="T24" s="80">
-        <v>2369</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="49">
-        <v>13</v>
-      </c>
-      <c r="B25" s="4">
-        <v>43902.625</v>
-      </c>
-      <c r="C25" s="84" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="84">
-        <v>1</v>
-      </c>
-      <c r="E25" s="84">
-        <v>1</v>
-      </c>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84">
-        <v>3</v>
-      </c>
-      <c r="N25" s="84"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
-      <c r="S25" s="84"/>
-      <c r="T25" s="84">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="49">
-        <v>13</v>
-      </c>
-      <c r="B26" s="4">
-        <v>43902.625</v>
-      </c>
-      <c r="C26" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="84">
-        <v>331</v>
-      </c>
-      <c r="E26" s="84">
-        <v>317</v>
-      </c>
-      <c r="F26" s="84">
-        <v>137</v>
-      </c>
-      <c r="G26" s="84">
-        <v>23</v>
-      </c>
-      <c r="H26" s="84">
-        <v>35</v>
-      </c>
-      <c r="I26" s="84">
-        <v>60</v>
-      </c>
-      <c r="J26" s="84">
-        <v>59</v>
-      </c>
-      <c r="K26" s="84">
-        <v>16</v>
-      </c>
-      <c r="L26" s="84">
-        <v>81</v>
-      </c>
-      <c r="M26" s="84">
-        <v>688</v>
-      </c>
-      <c r="N26" s="84">
-        <v>52</v>
-      </c>
-      <c r="O26" s="84">
-        <v>8</v>
-      </c>
-      <c r="P26" s="84">
-        <v>30</v>
-      </c>
-      <c r="Q26" s="84">
-        <v>14</v>
-      </c>
-      <c r="R26" s="84">
-        <v>29</v>
-      </c>
-      <c r="S26" s="84">
-        <v>12</v>
-      </c>
-      <c r="T26" s="84">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="49">
-        <v>13</v>
-      </c>
-      <c r="B27" s="4">
-        <v>43902.625</v>
-      </c>
-      <c r="C27" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="84">
-        <v>1</v>
-      </c>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84">
-        <v>2</v>
-      </c>
-      <c r="N27" s="84"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="84"/>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="84"/>
-      <c r="S27" s="84"/>
-      <c r="T27" s="84">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="49">
-        <v>14</v>
-      </c>
-      <c r="B28" s="4">
-        <v>43903.625</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="66">
-        <v>454</v>
-      </c>
-      <c r="E28" s="66">
-        <v>558</v>
-      </c>
-      <c r="F28" s="66">
-        <v>174</v>
-      </c>
-      <c r="G28" s="66">
-        <v>44</v>
-      </c>
-      <c r="H28" s="66">
-        <v>42</v>
-      </c>
-      <c r="I28" s="66">
-        <v>99</v>
-      </c>
-      <c r="J28" s="66">
-        <v>148</v>
-      </c>
-      <c r="K28" s="66">
-        <v>33</v>
-      </c>
-      <c r="L28" s="66">
-        <v>230</v>
-      </c>
-      <c r="M28" s="66">
-        <v>936</v>
-      </c>
-      <c r="N28" s="66">
-        <v>102</v>
-      </c>
-      <c r="O28" s="66">
-        <v>40</v>
-      </c>
-      <c r="P28" s="66">
-        <v>83</v>
-      </c>
-      <c r="Q28" s="66">
-        <v>42</v>
-      </c>
-      <c r="R28" s="66">
-        <v>48</v>
-      </c>
-      <c r="S28" s="66">
-        <v>29</v>
-      </c>
-      <c r="T28" s="66">
-        <v>3062</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="49">
-        <v>14</v>
-      </c>
-      <c r="B29" s="4">
-        <v>43903.625</v>
-      </c>
-      <c r="C29" s="84" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="66">
-        <v>1</v>
-      </c>
-      <c r="E29" s="66">
-        <v>1</v>
-      </c>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66">
-        <v>3</v>
-      </c>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="49">
-        <v>14</v>
-      </c>
-      <c r="B30" s="4">
-        <v>43903.625</v>
-      </c>
-      <c r="C30" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="66">
-        <v>401</v>
-      </c>
-      <c r="E30" s="66">
-        <v>412</v>
-      </c>
-      <c r="F30" s="66">
-        <v>174</v>
-      </c>
-      <c r="G30" s="66">
-        <v>44</v>
-      </c>
-      <c r="H30" s="66">
-        <v>42</v>
-      </c>
-      <c r="I30" s="66">
-        <v>99</v>
-      </c>
-      <c r="J30" s="66">
-        <v>94</v>
-      </c>
-      <c r="K30" s="66">
-        <v>21</v>
-      </c>
-      <c r="L30" s="66">
-        <v>134</v>
-      </c>
-      <c r="M30" s="66">
-        <v>887</v>
-      </c>
-      <c r="N30" s="66">
-        <v>102</v>
-      </c>
-      <c r="O30" s="66">
-        <v>30</v>
-      </c>
-      <c r="P30" s="66">
-        <v>46</v>
-      </c>
-      <c r="Q30" s="66">
-        <v>29</v>
-      </c>
-      <c r="R30" s="66">
-        <v>45</v>
-      </c>
-      <c r="S30" s="66">
-        <v>16</v>
-      </c>
-      <c r="T30" s="66">
-        <v>2576</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="49">
-        <v>14</v>
-      </c>
-      <c r="B31" s="4">
-        <v>43903.625</v>
-      </c>
-      <c r="C31" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="66">
-        <v>1</v>
-      </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="66">
-        <v>3</v>
-      </c>
-      <c r="N31" s="66"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="49">
-        <v>15</v>
-      </c>
-      <c r="B32" s="4">
-        <v>43904.625</v>
-      </c>
-      <c r="C32" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="66">
-        <v>569</v>
-      </c>
-      <c r="E32" s="66">
-        <v>681</v>
-      </c>
-      <c r="F32" s="66">
-        <v>216</v>
-      </c>
-      <c r="G32" s="66">
-        <v>61</v>
-      </c>
-      <c r="H32" s="66">
-        <v>50</v>
-      </c>
-      <c r="I32" s="66">
-        <v>158</v>
-      </c>
-      <c r="J32" s="66">
-        <v>203</v>
-      </c>
-      <c r="K32" s="66">
-        <v>45</v>
-      </c>
-      <c r="L32" s="66">
-        <v>253</v>
-      </c>
-      <c r="M32" s="66">
-        <v>1154</v>
-      </c>
-      <c r="N32" s="66">
-        <v>121</v>
-      </c>
-      <c r="O32" s="66">
-        <v>40</v>
-      </c>
-      <c r="P32" s="66">
-        <v>93</v>
-      </c>
-      <c r="Q32" s="66">
-        <v>45</v>
-      </c>
-      <c r="R32" s="66">
-        <v>60</v>
-      </c>
-      <c r="S32" s="66">
-        <v>46</v>
-      </c>
-      <c r="T32" s="66">
-        <v>3795</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="49">
-        <v>15</v>
-      </c>
-      <c r="B33" s="4">
-        <v>43904.625</v>
-      </c>
-      <c r="C33" s="84" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="66">
-        <v>2</v>
-      </c>
-      <c r="E33" s="66">
-        <v>1</v>
-      </c>
-      <c r="F33" s="66"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="66"/>
-      <c r="M33" s="66">
-        <v>5</v>
-      </c>
-      <c r="N33" s="66"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="49">
-        <v>15</v>
-      </c>
-      <c r="B34" s="4">
-        <v>43904.625</v>
-      </c>
-      <c r="C34" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="66">
-        <v>506</v>
-      </c>
-      <c r="E34" s="66">
-        <v>605</v>
-      </c>
-      <c r="F34" s="66">
-        <v>216</v>
-      </c>
-      <c r="G34" s="66">
-        <v>57</v>
-      </c>
-      <c r="H34" s="66">
-        <v>50</v>
-      </c>
-      <c r="I34" s="66">
-        <v>119</v>
-      </c>
-      <c r="J34" s="66">
-        <v>141</v>
-      </c>
-      <c r="K34" s="66">
-        <v>23</v>
-      </c>
-      <c r="L34" s="66">
-        <v>187</v>
-      </c>
-      <c r="M34" s="66">
-        <v>1154</v>
-      </c>
-      <c r="N34" s="66">
-        <v>121</v>
-      </c>
-      <c r="O34" s="66">
-        <v>31</v>
-      </c>
-      <c r="P34" s="66">
-        <v>86</v>
-      </c>
-      <c r="Q34" s="66">
-        <v>40</v>
-      </c>
-      <c r="R34" s="66">
-        <v>54</v>
-      </c>
-      <c r="S34" s="66">
-        <v>31</v>
-      </c>
-      <c r="T34" s="66">
-        <v>3421</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="49">
-        <v>15</v>
-      </c>
-      <c r="B35" s="4">
-        <v>43904.625</v>
-      </c>
-      <c r="C35" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="66">
-        <v>2</v>
-      </c>
-      <c r="E35" s="66">
-        <v>1</v>
-      </c>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="66">
-        <v>5</v>
-      </c>
-      <c r="N35" s="66"/>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="66"/>
-      <c r="S35" s="66"/>
-      <c r="T35" s="66">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="49">
-        <v>16</v>
-      </c>
-      <c r="B36" s="4">
-        <v>43905.625</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="49">
-        <v>827</v>
-      </c>
-      <c r="E36" s="49">
-        <v>886</v>
-      </c>
-      <c r="F36" s="49">
-        <v>265</v>
-      </c>
-      <c r="G36" s="49">
-        <v>84</v>
-      </c>
-      <c r="H36" s="49">
-        <v>53</v>
-      </c>
-      <c r="I36" s="49">
-        <v>162</v>
-      </c>
-      <c r="J36" s="49">
-        <v>286</v>
-      </c>
-      <c r="K36" s="49">
-        <v>50</v>
-      </c>
-      <c r="L36" s="49">
-        <v>287</v>
-      </c>
-      <c r="M36" s="49">
-        <v>1407</v>
-      </c>
-      <c r="N36" s="49">
-        <v>168</v>
-      </c>
-      <c r="O36" s="49">
-        <v>32</v>
-      </c>
-      <c r="P36" s="49">
-        <v>130</v>
-      </c>
-      <c r="Q36" s="49">
-        <v>47</v>
-      </c>
-      <c r="R36" s="49">
-        <v>103</v>
-      </c>
-      <c r="S36" s="49">
-        <v>51</v>
-      </c>
-      <c r="T36" s="49">
-        <v>4838</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="49">
-        <v>16</v>
-      </c>
-      <c r="B37" s="4">
-        <v>43905.625</v>
-      </c>
-      <c r="C37" s="84" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49">
-        <v>3</v>
-      </c>
-      <c r="E37" s="49">
-        <v>4</v>
-      </c>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49">
-        <v>5</v>
-      </c>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
-      <c r="A38" s="49">
-        <v>16</v>
-      </c>
-      <c r="B38" s="4">
-        <v>43905.625</v>
-      </c>
-      <c r="C38" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="49">
-        <v>524</v>
-      </c>
-      <c r="E38" s="49">
-        <v>804</v>
-      </c>
-      <c r="F38" s="49">
-        <v>265</v>
-      </c>
-      <c r="G38" s="49">
-        <v>56</v>
-      </c>
-      <c r="H38" s="49">
-        <v>53</v>
-      </c>
-      <c r="I38" s="49">
-        <v>162</v>
-      </c>
-      <c r="J38" s="49">
-        <v>207</v>
-      </c>
-      <c r="K38" s="49">
-        <v>33</v>
-      </c>
-      <c r="L38" s="49">
-        <v>238</v>
-      </c>
-      <c r="M38" s="49">
-        <v>1407</v>
-      </c>
-      <c r="N38" s="49">
-        <v>168</v>
-      </c>
-      <c r="O38" s="49">
-        <v>32</v>
-      </c>
-      <c r="P38" s="49">
-        <v>91</v>
-      </c>
-      <c r="Q38" s="49">
-        <v>40</v>
-      </c>
-      <c r="R38" s="49">
-        <v>79</v>
-      </c>
-      <c r="S38" s="49">
-        <v>36</v>
-      </c>
-      <c r="T38" s="49">
-        <v>4195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
-      <c r="A39" s="49">
-        <v>16</v>
-      </c>
-      <c r="B39" s="4">
-        <v>43905.625</v>
-      </c>
-      <c r="C39" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="49">
-        <v>2</v>
-      </c>
-      <c r="E39" s="49">
-        <v>1</v>
-      </c>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49">
-        <v>5</v>
-      </c>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
-      <c r="A40" s="49">
-        <v>17</v>
-      </c>
-      <c r="B40" s="4">
-        <v>43906.625</v>
-      </c>
-      <c r="C40" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="49">
-        <v>1105</v>
-      </c>
-      <c r="E40" s="49">
-        <v>1067</v>
-      </c>
-      <c r="F40" s="49">
-        <v>300</v>
-      </c>
-      <c r="G40" s="49">
-        <v>94</v>
-      </c>
-      <c r="H40" s="49">
-        <v>56</v>
-      </c>
-      <c r="I40" s="49">
-        <v>260</v>
-      </c>
-      <c r="J40" s="49">
-        <v>342</v>
-      </c>
-      <c r="K40" s="49">
-        <v>51</v>
-      </c>
-      <c r="L40" s="49">
-        <v>391</v>
-      </c>
-      <c r="M40" s="49">
-        <v>1541</v>
-      </c>
-      <c r="N40" s="49">
-        <v>325</v>
-      </c>
-      <c r="O40" s="49">
-        <v>85</v>
-      </c>
-      <c r="P40" s="49">
-        <v>140</v>
-      </c>
-      <c r="Q40" s="49">
-        <v>77</v>
-      </c>
-      <c r="R40" s="49">
-        <v>123</v>
-      </c>
-      <c r="S40" s="49">
-        <v>55</v>
-      </c>
-      <c r="T40" s="49">
-        <v>6012</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
-      <c r="A41" s="49">
-        <v>17</v>
-      </c>
-      <c r="B41" s="4">
-        <v>43906.625</v>
-      </c>
-      <c r="C41" s="84" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="49">
-        <v>3</v>
-      </c>
-      <c r="E41" s="49">
-        <v>5</v>
-      </c>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="49">
-        <v>5</v>
-      </c>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
-      <c r="P41" s="49"/>
-      <c r="Q41" s="49"/>
-      <c r="R41" s="49"/>
-      <c r="S41" s="49"/>
-      <c r="T41" s="49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
-      <c r="A42" s="49">
-        <v>17</v>
-      </c>
-      <c r="B42" s="4">
-        <v>43906.625</v>
-      </c>
-      <c r="C42" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="49">
-        <v>1062</v>
-      </c>
-      <c r="E42" s="49">
-        <v>965</v>
-      </c>
-      <c r="F42" s="49">
-        <v>300</v>
-      </c>
-      <c r="G42" s="49">
-        <v>65</v>
-      </c>
-      <c r="H42" s="49">
-        <v>56</v>
-      </c>
-      <c r="I42" s="49">
-        <v>255</v>
-      </c>
-      <c r="J42" s="49">
-        <v>241</v>
-      </c>
-      <c r="K42" s="49">
-        <v>36</v>
-      </c>
-      <c r="L42" s="49">
-        <v>272</v>
-      </c>
-      <c r="M42" s="49">
-        <v>1541</v>
-      </c>
-      <c r="N42" s="49">
-        <v>325</v>
-      </c>
-      <c r="O42" s="49">
-        <v>32</v>
-      </c>
-      <c r="P42" s="49">
-        <v>103</v>
-      </c>
-      <c r="Q42" s="49">
-        <v>40</v>
-      </c>
-      <c r="R42" s="49">
-        <v>104</v>
-      </c>
-      <c r="S42" s="49">
-        <v>36</v>
-      </c>
-      <c r="T42" s="49">
-        <v>5433</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
-      <c r="A43" s="49">
-        <v>17</v>
-      </c>
-      <c r="B43" s="4">
-        <v>43906.625</v>
-      </c>
-      <c r="C43" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="49">
-        <v>3</v>
-      </c>
-      <c r="E43" s="49">
-        <v>4</v>
-      </c>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49">
-        <v>5</v>
-      </c>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="49"/>
-      <c r="T43" s="49">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
-      <c r="A44" s="49">
-        <v>18</v>
-      </c>
-      <c r="B44" s="4">
-        <v>43907.625</v>
-      </c>
-      <c r="C44" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="66">
-        <v>1479</v>
-      </c>
-      <c r="E44" s="66">
-        <v>1109</v>
-      </c>
-      <c r="F44" s="66">
-        <v>345</v>
-      </c>
-      <c r="G44" s="66">
-        <v>73</v>
-      </c>
-      <c r="H44" s="66">
-        <v>57</v>
-      </c>
-      <c r="I44" s="66">
-        <v>310</v>
-      </c>
-      <c r="J44" s="66">
-        <v>373</v>
-      </c>
-      <c r="K44" s="66">
-        <v>45</v>
-      </c>
-      <c r="L44" s="66">
-        <v>325</v>
-      </c>
-      <c r="M44" s="66">
-        <v>2105</v>
-      </c>
-      <c r="N44" s="66">
-        <v>442</v>
-      </c>
-      <c r="O44" s="66">
-        <v>75</v>
-      </c>
-      <c r="P44" s="66">
-        <v>182</v>
-      </c>
-      <c r="Q44" s="66">
-        <v>58</v>
-      </c>
-      <c r="R44" s="66">
-        <v>127</v>
-      </c>
-      <c r="S44" s="66">
-        <v>51</v>
-      </c>
-      <c r="T44" s="66">
-        <v>7156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
-      <c r="A45" s="49">
-        <v>18</v>
-      </c>
-      <c r="B45" s="4">
-        <v>43907.625</v>
-      </c>
-      <c r="C45" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" s="66">
-        <v>2</v>
-      </c>
-      <c r="E45" s="66">
-        <v>4</v>
-      </c>
-      <c r="F45" s="66">
-        <v>0</v>
-      </c>
-      <c r="G45" s="66">
-        <v>0</v>
-      </c>
-      <c r="H45" s="66">
-        <v>0</v>
-      </c>
-      <c r="I45" s="66">
-        <v>0</v>
-      </c>
-      <c r="J45" s="66">
-        <v>0</v>
-      </c>
-      <c r="K45" s="66">
-        <v>0</v>
-      </c>
-      <c r="L45" s="66">
-        <v>0</v>
-      </c>
-      <c r="M45" s="66">
-        <v>6</v>
-      </c>
-      <c r="N45" s="66">
-        <v>0</v>
-      </c>
-      <c r="O45" s="66">
-        <v>0</v>
-      </c>
-      <c r="P45" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="66">
-        <v>0</v>
-      </c>
-      <c r="R45" s="66">
-        <v>0</v>
-      </c>
-      <c r="S45" s="66">
-        <v>0</v>
-      </c>
-      <c r="T45" s="66">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="49">
-        <v>19</v>
-      </c>
-      <c r="B46" s="86">
-        <v>43908</v>
-      </c>
-      <c r="C46" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="66">
-        <v>1609</v>
-      </c>
-      <c r="E46" s="66">
-        <v>1243</v>
-      </c>
-      <c r="F46" s="66">
-        <v>391</v>
-      </c>
-      <c r="G46" s="66">
-        <v>92</v>
-      </c>
-      <c r="H46" s="66">
-        <v>69</v>
-      </c>
-      <c r="I46" s="66">
-        <v>358</v>
-      </c>
-      <c r="J46" s="66">
-        <v>432</v>
-      </c>
-      <c r="K46" s="66">
-        <v>56</v>
-      </c>
-      <c r="L46" s="66">
-        <v>478</v>
-      </c>
-      <c r="M46" s="66">
-        <v>2372</v>
-      </c>
-      <c r="N46" s="66">
-        <v>474</v>
-      </c>
-      <c r="O46" s="66">
-        <v>88</v>
-      </c>
-      <c r="P46" s="66">
-        <v>198</v>
-      </c>
-      <c r="Q46" s="66">
-        <v>105</v>
-      </c>
-      <c r="R46" s="66">
-        <v>159</v>
-      </c>
-      <c r="S46" s="66">
-        <v>74</v>
-      </c>
-      <c r="T46" s="66">
-        <v>8198</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47" s="49">
-        <v>19</v>
-      </c>
-      <c r="B47" s="86">
-        <v>43908</v>
-      </c>
-      <c r="C47" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" s="66">
-        <v>2</v>
-      </c>
-      <c r="E47" s="66">
-        <v>4</v>
-      </c>
-      <c r="F47" s="66">
-        <v>0</v>
-      </c>
-      <c r="G47" s="66">
-        <v>0</v>
-      </c>
-      <c r="H47" s="66">
-        <v>0</v>
-      </c>
-      <c r="I47" s="66">
-        <v>0</v>
-      </c>
-      <c r="J47" s="66">
-        <v>0</v>
-      </c>
-      <c r="K47" s="66">
-        <v>0</v>
-      </c>
-      <c r="L47" s="66">
-        <v>0</v>
-      </c>
-      <c r="M47" s="66">
-        <v>6</v>
-      </c>
-      <c r="N47" s="66">
-        <v>0</v>
-      </c>
-      <c r="O47" s="66">
-        <v>0</v>
-      </c>
-      <c r="P47" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="66">
-        <v>0</v>
-      </c>
-      <c r="R47" s="66">
-        <v>0</v>
-      </c>
-      <c r="S47" s="66">
-        <v>0</v>
-      </c>
-      <c r="T47" s="66">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48" s="49">
-        <v>20</v>
-      </c>
-      <c r="B48" s="86">
-        <v>43909</v>
-      </c>
-      <c r="C48" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="49">
-        <v>2155</v>
-      </c>
-      <c r="E48" s="49">
-        <v>1692</v>
-      </c>
-      <c r="F48" s="49">
-        <v>573</v>
-      </c>
-      <c r="G48" s="49">
-        <v>134</v>
-      </c>
-      <c r="H48" s="49">
-        <v>80</v>
-      </c>
-      <c r="I48" s="49">
-        <v>432</v>
-      </c>
-      <c r="J48" s="49">
-        <v>682</v>
-      </c>
-      <c r="K48" s="49">
-        <v>98</v>
-      </c>
-      <c r="L48" s="49">
-        <v>669</v>
-      </c>
-      <c r="M48" s="49">
-        <v>3033</v>
-      </c>
-      <c r="N48" s="49">
-        <v>637</v>
-      </c>
-      <c r="O48" s="49">
-        <v>99</v>
-      </c>
-      <c r="P48" s="49">
-        <v>275</v>
-      </c>
-      <c r="Q48" s="49">
-        <v>140</v>
-      </c>
-      <c r="R48" s="49">
-        <v>202</v>
-      </c>
-      <c r="S48" s="49">
-        <v>98</v>
-      </c>
-      <c r="T48" s="49">
-        <v>10999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
-      <c r="A49" s="49">
-        <v>20</v>
-      </c>
-      <c r="B49" s="86">
-        <v>43909</v>
-      </c>
-      <c r="C49" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D49" s="49">
-        <v>6</v>
-      </c>
-      <c r="E49" s="49">
-        <v>8</v>
-      </c>
-      <c r="F49" s="49">
-        <v>0</v>
-      </c>
-      <c r="G49" s="49">
-        <v>0</v>
-      </c>
-      <c r="H49" s="49">
-        <v>0</v>
-      </c>
-      <c r="I49" s="49">
-        <v>0</v>
-      </c>
-      <c r="J49" s="49">
-        <v>0</v>
-      </c>
-      <c r="K49" s="49">
-        <v>0</v>
-      </c>
-      <c r="L49" s="49">
-        <v>0</v>
-      </c>
-      <c r="M49" s="49">
-        <v>6</v>
-      </c>
-      <c r="N49" s="49">
-        <v>0</v>
-      </c>
-      <c r="O49" s="49">
-        <v>0</v>
-      </c>
-      <c r="P49" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="49">
-        <v>0</v>
-      </c>
-      <c r="R49" s="49">
-        <v>0</v>
-      </c>
-      <c r="S49" s="49">
-        <v>0</v>
-      </c>
-      <c r="T49" s="49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50" s="49">
-        <v>21</v>
-      </c>
-      <c r="B50" s="86">
-        <v>43910</v>
-      </c>
-      <c r="C50" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D50" s="66">
-        <v>2746</v>
-      </c>
-      <c r="E50" s="66">
-        <v>2401</v>
-      </c>
-      <c r="F50" s="66">
-        <v>731</v>
-      </c>
-      <c r="G50" s="66">
-        <v>192</v>
-      </c>
-      <c r="H50" s="66">
-        <v>121</v>
-      </c>
-      <c r="I50" s="66">
-        <v>586</v>
-      </c>
-      <c r="J50" s="66">
-        <v>813</v>
-      </c>
-      <c r="K50" s="66">
-        <v>131</v>
-      </c>
-      <c r="L50" s="66">
-        <v>803</v>
-      </c>
-      <c r="M50" s="66">
-        <v>3497</v>
-      </c>
-      <c r="N50" s="66">
-        <v>801</v>
-      </c>
-      <c r="O50" s="66">
-        <v>146</v>
-      </c>
-      <c r="P50" s="66">
-        <v>394</v>
-      </c>
-      <c r="Q50" s="66">
-        <v>180</v>
-      </c>
-      <c r="R50" s="66">
-        <v>266</v>
-      </c>
-      <c r="S50" s="66">
-        <v>149</v>
-      </c>
-      <c r="T50" s="66">
-        <v>13957</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
-      <c r="A51" s="49">
-        <v>21</v>
-      </c>
-      <c r="B51" s="86">
-        <v>43910</v>
-      </c>
-      <c r="C51" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D51" s="66">
-        <v>10</v>
-      </c>
-      <c r="E51" s="66">
-        <v>12</v>
-      </c>
-      <c r="F51" s="66">
-        <v>0</v>
-      </c>
-      <c r="G51" s="66">
-        <v>0</v>
-      </c>
-      <c r="H51" s="66">
-        <v>0</v>
-      </c>
-      <c r="I51" s="66">
-        <v>0</v>
-      </c>
-      <c r="J51" s="66">
-        <v>1</v>
-      </c>
-      <c r="K51" s="66">
-        <v>0</v>
-      </c>
-      <c r="L51" s="66">
-        <v>0</v>
-      </c>
-      <c r="M51" s="66">
-        <v>6</v>
-      </c>
-      <c r="N51" s="66">
-        <v>1</v>
-      </c>
-      <c r="O51" s="66">
-        <v>0</v>
-      </c>
-      <c r="P51" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="66">
-        <v>0</v>
-      </c>
-      <c r="R51" s="66">
-        <v>1</v>
-      </c>
-      <c r="S51" s="66">
-        <v>0</v>
-      </c>
-      <c r="T51" s="66">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E67D7-4FF2-D745-A107-DDC4CB6E1273}">
-  <dimension ref="A1:Z24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="3.6640625" style="51" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="19" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" style="13" customWidth="1"/>
-    <col min="25" max="25" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="120.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" s="24" customFormat="1" ht="109">
-      <c r="A1" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="U1" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="V1" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="W1" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26">
-      <c r="A2" s="69">
-        <f t="shared" ref="A2:A17" si="0">A3-1</f>
-        <v>-22</v>
-      </c>
-      <c r="B2" s="15">
-        <v>43889.416666666664</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>25</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="T2" s="48">
-        <v>53</v>
-      </c>
-      <c r="U2" s="34" t="str">
-        <f t="shared" ref="U2:U14" si="1">IF(ISNUMBER(T1),T2-T1,"")</f>
-        <v/>
-      </c>
-      <c r="V2" s="12" t="str">
-        <f t="shared" ref="V2:V15" si="2">IF(ISNUMBER(T1),
-((T2-T1)/T1)/(B2-B1),
-"")</f>
-        <v/>
-      </c>
-      <c r="W2" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>56.879209835213864</v>
-      </c>
-      <c r="Z2" s="87"/>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="69">
-        <f t="shared" si="0"/>
-        <v>-21</v>
-      </c>
-      <c r="B3" s="15">
-        <v>43890.416666666664</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>15</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="T3" s="48">
-        <v>66</v>
-      </c>
-      <c r="U3" s="34">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V3" s="12">
-        <f t="shared" si="2"/>
-        <v>0.24528301886792453</v>
-      </c>
-      <c r="W3" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>71.663313772773421</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z3" s="50">
-        <f>last_DE_Total*0.5</f>
-        <v>8331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="69">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
-      <c r="B4" s="15">
-        <v>43891.625</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>74</v>
-      </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>2</v>
-      </c>
-      <c r="T4" s="48">
-        <v>129</v>
-      </c>
-      <c r="U4" s="34">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="V4" s="12">
-        <f t="shared" si="2"/>
-        <v>0.78996865203603195</v>
-      </c>
-      <c r="W4" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>94.742552080142715</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z4" s="50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="69">
-        <f t="shared" si="0"/>
-        <v>-19</v>
-      </c>
-      <c r="B5" s="15">
-        <v>43892.625</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>26</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>90</v>
-      </c>
-      <c r="N5">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>2</v>
-      </c>
-      <c r="T5" s="48">
-        <v>157</v>
-      </c>
-      <c r="U5" s="34">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="V5" s="12">
-        <f t="shared" si="2"/>
-        <v>0.21705426356589147</v>
-      </c>
-      <c r="W5" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>119.36813568653308</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="69">
-        <f t="shared" si="0"/>
-        <v>-18</v>
-      </c>
-      <c r="B6" s="15">
-        <v>43893.625</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>37</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>103</v>
-      </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>2</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6" s="48">
-        <v>196</v>
-      </c>
-      <c r="U6" s="34">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="V6" s="12">
-        <f t="shared" si="2"/>
-        <v>0.24840764331210191</v>
-      </c>
-      <c r="W6" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>150.3944268381704</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="69">
-        <f t="shared" si="0"/>
-        <v>-17</v>
-      </c>
-      <c r="B7" s="15">
-        <v>43894.625</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>48</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>115</v>
-      </c>
-      <c r="N7">
-        <v>7</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>2</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7" s="48">
-        <v>262</v>
-      </c>
-      <c r="U7" s="34">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="V7" s="12">
-        <f t="shared" si="2"/>
-        <v>0.33673469387755101</v>
-      </c>
-      <c r="W7" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>189.48510416028546</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="69">
-        <f t="shared" si="0"/>
-        <v>-16</v>
-      </c>
-      <c r="B8" s="15">
-        <v>43895.625</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>73</v>
-      </c>
-      <c r="E8">
-        <v>70</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>181</v>
-      </c>
-      <c r="N8">
-        <v>8</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>7</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" s="48">
-        <v>400</v>
-      </c>
-      <c r="U8" s="34">
-        <f t="shared" si="1"/>
-        <v>138</v>
-      </c>
-      <c r="V8" s="12">
-        <f t="shared" si="2"/>
-        <v>0.52671755725190839</v>
-      </c>
-      <c r="W8" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>238.73627137306619</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="69">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="B9" s="15">
-        <v>43896.625</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="3">
-        <v>96</v>
-      </c>
-      <c r="E9" s="3">
-        <v>117</v>
-      </c>
-      <c r="F9" s="3">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3">
-        <v>11</v>
-      </c>
-      <c r="J9" s="3">
-        <v>16</v>
-      </c>
-      <c r="K9" s="3">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
-        <v>18</v>
-      </c>
-      <c r="M9" s="3">
-        <v>329</v>
-      </c>
-      <c r="N9" s="3">
-        <v>10</v>
-      </c>
-      <c r="O9" s="3">
-        <v>2</v>
-      </c>
-      <c r="P9" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3">
-        <v>7</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1</v>
-      </c>
-      <c r="T9" s="48">
-        <v>639</v>
-      </c>
-      <c r="U9" s="36">
-        <f t="shared" si="1"/>
-        <v>239</v>
-      </c>
-      <c r="V9" s="12">
-        <f t="shared" si="2"/>
-        <v>0.59750000000000003</v>
-      </c>
-      <c r="W9" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>300.78885367634092</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="69">
-        <f t="shared" si="0"/>
-        <v>-14</v>
-      </c>
-      <c r="B10" s="15">
-        <v>43897.625</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>170</v>
-      </c>
-      <c r="E10">
-        <v>134</v>
-      </c>
-      <c r="F10">
-        <v>28</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10">
-        <v>13</v>
-      </c>
-      <c r="J10">
-        <v>17</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-      <c r="L10">
-        <v>19</v>
-      </c>
-      <c r="M10">
-        <v>373</v>
-      </c>
-      <c r="N10">
-        <v>13</v>
-      </c>
-      <c r="O10">
-        <v>3</v>
-      </c>
-      <c r="P10">
-        <v>4</v>
-      </c>
-      <c r="R10">
-        <v>8</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-      <c r="T10" s="48">
-        <v>795</v>
-      </c>
-      <c r="U10" s="34">
-        <f t="shared" si="1"/>
-        <v>156</v>
-      </c>
-      <c r="V10" s="12">
-        <f t="shared" si="2"/>
-        <v>0.24413145539906103</v>
-      </c>
-      <c r="W10" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>378.97020832057075</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="69">
-        <f t="shared" si="0"/>
-        <v>-13</v>
-      </c>
-      <c r="B11" s="15">
-        <v>43898.625</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11">
-        <v>182</v>
-      </c>
-      <c r="E11">
-        <v>172</v>
-      </c>
-      <c r="F11">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11">
-        <v>13</v>
-      </c>
-      <c r="J11">
-        <v>19</v>
-      </c>
-      <c r="K11">
-        <v>8</v>
-      </c>
-      <c r="L11">
-        <v>21</v>
-      </c>
-      <c r="M11">
-        <v>398</v>
-      </c>
-      <c r="N11">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-      <c r="P11">
-        <v>7</v>
-      </c>
-      <c r="R11">
-        <v>9</v>
-      </c>
-      <c r="S11">
-        <v>2</v>
-      </c>
-      <c r="T11" s="48">
-        <v>902</v>
-      </c>
-      <c r="U11" s="34">
-        <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="V11" s="12">
-        <f t="shared" si="2"/>
-        <v>0.13459119496855346</v>
-      </c>
-      <c r="W11" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>477.47254274613243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="69">
-        <f t="shared" si="0"/>
-        <v>-12</v>
-      </c>
-      <c r="B12" s="15">
-        <v>43899.625</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12">
-        <v>204</v>
-      </c>
-      <c r="E12">
-        <v>256</v>
-      </c>
-      <c r="F12">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-      <c r="H12">
-        <v>4</v>
-      </c>
-      <c r="I12">
-        <v>17</v>
-      </c>
-      <c r="J12">
-        <v>26</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>38</v>
-      </c>
-      <c r="M12">
-        <v>484</v>
-      </c>
-      <c r="N12">
-        <v>17</v>
-      </c>
-      <c r="O12">
-        <v>6</v>
-      </c>
-      <c r="P12">
-        <v>12</v>
-      </c>
-      <c r="R12">
-        <v>9</v>
-      </c>
-      <c r="S12">
-        <v>2</v>
-      </c>
-      <c r="T12" s="48">
-        <v>1139</v>
-      </c>
-      <c r="U12" s="34">
-        <f t="shared" si="1"/>
-        <v>237</v>
-      </c>
-      <c r="V12" s="12">
-        <f t="shared" si="2"/>
-        <v>0.26274944567627495</v>
-      </c>
-      <c r="W12" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>601.57770735268173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="69">
-        <f t="shared" si="0"/>
-        <v>-11</v>
-      </c>
-      <c r="B13" s="15">
-        <v>43900.625</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13">
-        <v>237</v>
-      </c>
-      <c r="E13">
-        <v>314</v>
-      </c>
-      <c r="F13">
-        <v>48</v>
-      </c>
-      <c r="G13">
-        <v>9</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
-      <c r="I13">
-        <v>29</v>
-      </c>
-      <c r="J13">
-        <v>35</v>
-      </c>
-      <c r="K13">
-        <v>13</v>
-      </c>
-      <c r="L13">
-        <v>49</v>
-      </c>
-      <c r="M13">
-        <v>484</v>
-      </c>
-      <c r="N13">
-        <v>25</v>
-      </c>
-      <c r="O13">
-        <v>7</v>
-      </c>
-      <c r="P13">
-        <v>22</v>
-      </c>
-      <c r="Q13">
-        <v>7</v>
-      </c>
-      <c r="R13">
-        <v>9</v>
-      </c>
-      <c r="S13">
-        <v>4</v>
-      </c>
-      <c r="T13" s="48">
-        <v>1296</v>
-      </c>
-      <c r="U13" s="34">
-        <f t="shared" si="1"/>
-        <v>157</v>
-      </c>
-      <c r="V13" s="12">
-        <f t="shared" si="2"/>
-        <v>0.13784021071115013</v>
-      </c>
-      <c r="W13" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>757.94041664114161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="69">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="B14" s="15">
-        <v>43901.625</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14">
-        <v>277</v>
-      </c>
-      <c r="E14">
-        <v>366</v>
-      </c>
-      <c r="F14">
-        <v>90</v>
-      </c>
-      <c r="G14">
-        <v>24</v>
-      </c>
-      <c r="H14">
-        <v>21</v>
-      </c>
-      <c r="I14">
-        <v>48</v>
-      </c>
-      <c r="J14">
-        <v>48</v>
-      </c>
-      <c r="K14">
-        <v>17</v>
-      </c>
-      <c r="L14">
-        <v>75</v>
-      </c>
-      <c r="M14">
-        <v>484</v>
-      </c>
-      <c r="N14">
-        <v>25</v>
-      </c>
-      <c r="O14">
-        <v>14</v>
-      </c>
-      <c r="P14">
-        <v>26</v>
-      </c>
-      <c r="Q14">
-        <v>15</v>
-      </c>
-      <c r="R14">
-        <v>27</v>
-      </c>
-      <c r="S14">
-        <v>10</v>
-      </c>
-      <c r="T14" s="48">
-        <v>1567</v>
-      </c>
-      <c r="U14" s="34">
-        <f t="shared" si="1"/>
-        <v>271</v>
-      </c>
-      <c r="V14" s="12">
-        <f t="shared" si="2"/>
-        <v>0.20910493827160495</v>
-      </c>
-      <c r="W14" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>954.94508549226452</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="69">
-        <f t="shared" si="0"/>
-        <v>-9</v>
-      </c>
-      <c r="B15" s="16">
-        <v>43902.625</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="9">
-        <v>454</v>
-      </c>
-      <c r="E15" s="9">
-        <v>500</v>
-      </c>
-      <c r="F15" s="9">
-        <v>137</v>
-      </c>
-      <c r="G15" s="9">
-        <v>30</v>
-      </c>
-      <c r="H15" s="9">
-        <v>38</v>
-      </c>
-      <c r="I15" s="9">
-        <v>88</v>
-      </c>
-      <c r="J15" s="9">
-        <v>99</v>
-      </c>
-      <c r="K15" s="9">
-        <v>23</v>
-      </c>
-      <c r="L15" s="9">
-        <v>129</v>
-      </c>
-      <c r="M15" s="9">
-        <v>688</v>
-      </c>
-      <c r="N15" s="9">
-        <v>52</v>
-      </c>
-      <c r="O15" s="9">
-        <v>14</v>
-      </c>
-      <c r="P15" s="9">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>27</v>
-      </c>
-      <c r="R15" s="9">
-        <v>31</v>
-      </c>
-      <c r="S15" s="9">
-        <v>14</v>
-      </c>
-      <c r="T15" s="48">
-        <v>2369</v>
-      </c>
-      <c r="U15" s="38">
-        <f t="shared" ref="U15:U20" si="3">IF(ISNUMBER(T14),T15-T14,"")</f>
-        <v>802</v>
-      </c>
-      <c r="V15" s="39">
-        <f t="shared" si="2"/>
-        <v>0.51180599872367583</v>
-      </c>
-      <c r="W15" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>1203.1554147053635</v>
-      </c>
-      <c r="X15" s="40"/>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="69">
-        <f t="shared" si="0"/>
-        <v>-8</v>
-      </c>
-      <c r="B16" s="16">
-        <v>43903.625</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="46">
-        <v>454</v>
-      </c>
-      <c r="E16" s="46">
-        <v>558</v>
-      </c>
-      <c r="F16" s="46">
-        <v>174</v>
-      </c>
-      <c r="G16" s="46">
-        <v>44</v>
-      </c>
-      <c r="H16" s="46">
-        <v>42</v>
-      </c>
-      <c r="I16" s="46">
-        <v>99</v>
-      </c>
-      <c r="J16" s="46">
-        <v>148</v>
-      </c>
-      <c r="K16" s="46">
-        <v>33</v>
-      </c>
-      <c r="L16" s="46">
-        <v>230</v>
-      </c>
-      <c r="M16" s="46">
-        <v>936</v>
-      </c>
-      <c r="N16" s="46">
-        <v>102</v>
-      </c>
-      <c r="O16" s="46">
-        <v>40</v>
-      </c>
-      <c r="P16" s="46">
-        <v>83</v>
-      </c>
-      <c r="Q16" s="46">
-        <v>42</v>
-      </c>
-      <c r="R16" s="46">
-        <v>48</v>
-      </c>
-      <c r="S16" s="46">
-        <v>29</v>
-      </c>
-      <c r="T16" s="48">
-        <v>3062</v>
-      </c>
-      <c r="U16" s="38">
-        <f t="shared" si="3"/>
-        <v>693</v>
-      </c>
-      <c r="V16" s="39">
-        <f t="shared" ref="V16:V21" si="4">IF(ISNUMBER(T15),
-((T16-T15)/T15)/(B16-B15),
-"")</f>
-        <v>0.29252849303503586</v>
-      </c>
-      <c r="W16" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>1515.880833282283</v>
-      </c>
-      <c r="X16" s="40"/>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="69">
-        <f t="shared" si="0"/>
-        <v>-7</v>
-      </c>
-      <c r="B17" s="16">
-        <v>43904.625</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="48">
-        <v>569</v>
-      </c>
-      <c r="E17" s="48">
-        <v>681</v>
-      </c>
-      <c r="F17" s="48">
-        <v>216</v>
-      </c>
-      <c r="G17" s="48">
-        <v>61</v>
-      </c>
-      <c r="H17" s="48">
-        <v>50</v>
-      </c>
-      <c r="I17" s="48">
-        <v>158</v>
-      </c>
-      <c r="J17" s="48">
-        <v>203</v>
-      </c>
-      <c r="K17" s="48">
-        <v>45</v>
-      </c>
-      <c r="L17" s="48">
-        <v>253</v>
-      </c>
-      <c r="M17" s="48">
-        <v>1154</v>
-      </c>
-      <c r="N17" s="48">
-        <v>121</v>
-      </c>
-      <c r="O17" s="48">
-        <v>40</v>
-      </c>
-      <c r="P17" s="48">
-        <v>93</v>
-      </c>
-      <c r="Q17" s="48">
-        <v>45</v>
-      </c>
-      <c r="R17" s="48">
-        <v>60</v>
-      </c>
-      <c r="S17" s="48">
-        <v>46</v>
-      </c>
-      <c r="T17" s="48">
-        <v>3795</v>
-      </c>
-      <c r="U17" s="38">
-        <f t="shared" si="3"/>
-        <v>733</v>
-      </c>
-      <c r="V17" s="39">
-        <f t="shared" si="4"/>
-        <v>0.23938602220770738</v>
-      </c>
-      <c r="W17" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>1909.890170984529</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="69">
-        <f>A19-1</f>
-        <v>-6</v>
-      </c>
-      <c r="B18" s="37">
-        <v>43905.625</v>
-      </c>
-      <c r="C18" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="73">
-        <v>827</v>
-      </c>
-      <c r="E18" s="73">
-        <v>886</v>
-      </c>
-      <c r="F18" s="73">
-        <v>265</v>
-      </c>
-      <c r="G18" s="73">
-        <v>84</v>
-      </c>
-      <c r="H18" s="73">
-        <v>53</v>
-      </c>
-      <c r="I18" s="73">
-        <v>162</v>
-      </c>
-      <c r="J18" s="73">
-        <v>286</v>
-      </c>
-      <c r="K18" s="73">
-        <v>50</v>
-      </c>
-      <c r="L18" s="73">
-        <v>287</v>
-      </c>
-      <c r="M18" s="73">
-        <v>1407</v>
-      </c>
-      <c r="N18" s="73">
-        <v>168</v>
-      </c>
-      <c r="O18" s="73">
-        <v>32</v>
-      </c>
-      <c r="P18" s="73">
-        <v>130</v>
-      </c>
-      <c r="Q18" s="73">
-        <v>47</v>
-      </c>
-      <c r="R18" s="73">
-        <v>103</v>
-      </c>
-      <c r="S18" s="73">
-        <v>51</v>
-      </c>
-      <c r="T18" s="74">
-        <v>4838</v>
-      </c>
-      <c r="U18" s="38">
-        <f t="shared" si="3"/>
-        <v>1043</v>
-      </c>
-      <c r="V18" s="39">
-        <f t="shared" si="4"/>
-        <v>0.2748353096179183</v>
-      </c>
-      <c r="W18" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>2406.3108294107265</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="69">
-        <f>A20-1</f>
-        <v>-5</v>
-      </c>
-      <c r="B19" s="37">
-        <v>43906.625</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="49">
-        <v>1105</v>
-      </c>
-      <c r="E19" s="49">
-        <v>1067</v>
-      </c>
-      <c r="F19" s="49">
-        <v>300</v>
-      </c>
-      <c r="G19" s="49">
-        <v>94</v>
-      </c>
-      <c r="H19" s="49">
-        <v>56</v>
-      </c>
-      <c r="I19" s="49">
-        <v>260</v>
-      </c>
-      <c r="J19" s="49">
-        <v>342</v>
-      </c>
-      <c r="K19" s="49">
-        <v>51</v>
-      </c>
-      <c r="L19" s="49">
-        <v>391</v>
-      </c>
-      <c r="M19" s="49">
-        <v>1541</v>
-      </c>
-      <c r="N19" s="49">
-        <v>325</v>
-      </c>
-      <c r="O19" s="49">
-        <v>85</v>
-      </c>
-      <c r="P19" s="49">
-        <v>140</v>
-      </c>
-      <c r="Q19" s="49">
-        <v>77</v>
-      </c>
-      <c r="R19" s="49">
-        <v>123</v>
-      </c>
-      <c r="S19" s="49">
-        <v>55</v>
-      </c>
-      <c r="T19" s="49">
-        <v>6012</v>
-      </c>
-      <c r="U19" s="38">
-        <f t="shared" si="3"/>
-        <v>1174</v>
-      </c>
-      <c r="V19" s="39">
-        <f t="shared" si="4"/>
-        <v>0.24266225713104589</v>
-      </c>
-      <c r="W19" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>3031.7616665645664</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="69">
-        <f>A21-1</f>
-        <v>-4</v>
-      </c>
-      <c r="B20" s="37">
-        <v>43907.625</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="66">
-        <v>1479</v>
-      </c>
-      <c r="E20" s="66">
-        <v>1109</v>
-      </c>
-      <c r="F20" s="66">
-        <v>345</v>
-      </c>
-      <c r="G20" s="66">
-        <v>73</v>
-      </c>
-      <c r="H20" s="66">
-        <v>57</v>
-      </c>
-      <c r="I20" s="66">
-        <v>310</v>
-      </c>
-      <c r="J20" s="66">
-        <v>373</v>
-      </c>
-      <c r="K20" s="66">
-        <v>45</v>
-      </c>
-      <c r="L20" s="66">
-        <v>325</v>
-      </c>
-      <c r="M20" s="66">
-        <v>2105</v>
-      </c>
-      <c r="N20" s="66">
-        <v>442</v>
-      </c>
-      <c r="O20" s="66">
-        <v>75</v>
-      </c>
-      <c r="P20" s="66">
-        <v>182</v>
-      </c>
-      <c r="Q20" s="66">
-        <v>58</v>
-      </c>
-      <c r="R20" s="66">
-        <v>127</v>
-      </c>
-      <c r="S20" s="66">
-        <v>51</v>
-      </c>
-      <c r="T20" s="66">
-        <v>7156</v>
-      </c>
-      <c r="U20" s="38">
-        <f t="shared" si="3"/>
-        <v>1144</v>
-      </c>
-      <c r="V20" s="39">
-        <f t="shared" si="4"/>
-        <v>0.19028609447771125</v>
-      </c>
-      <c r="W20" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>3819.7803419690581</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="69">
-        <f>A22-1</f>
-        <v>-3</v>
-      </c>
-      <c r="B21" s="37">
-        <v>43908</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="48">
-        <v>1609</v>
-      </c>
-      <c r="E21" s="48">
-        <v>1243</v>
-      </c>
-      <c r="F21" s="48">
-        <v>391</v>
-      </c>
-      <c r="G21" s="48">
-        <v>92</v>
-      </c>
-      <c r="H21" s="48">
-        <v>69</v>
-      </c>
-      <c r="I21" s="48">
-        <v>358</v>
-      </c>
-      <c r="J21" s="48">
-        <v>432</v>
-      </c>
-      <c r="K21" s="48">
-        <v>56</v>
-      </c>
-      <c r="L21" s="48">
-        <v>478</v>
-      </c>
-      <c r="M21" s="48">
-        <v>2372</v>
-      </c>
-      <c r="N21" s="48">
-        <v>474</v>
-      </c>
-      <c r="O21" s="48">
-        <v>88</v>
-      </c>
-      <c r="P21" s="48">
-        <v>198</v>
-      </c>
-      <c r="Q21" s="48">
-        <v>105</v>
-      </c>
-      <c r="R21" s="48">
-        <v>159</v>
-      </c>
-      <c r="S21" s="48">
-        <v>74</v>
-      </c>
-      <c r="T21" s="48">
-        <v>8198</v>
-      </c>
-      <c r="U21" s="38">
-        <f>IF(ISNUMBER(T20),T21-T20,"")</f>
-        <v>1042</v>
-      </c>
-      <c r="V21" s="39">
-        <f t="shared" si="4"/>
-        <v>0.38829886342463205</v>
-      </c>
-      <c r="W21" s="70">
-        <f>guide_start*EXP((Table5[[#This Row],[Date]]-date_last_DE_Total)*(LN(2)/guide_doubling))</f>
-        <v>4165.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" s="69">
-        <f>A23-1</f>
-        <v>-2</v>
-      </c>
-      <c r="B22" s="89">
-        <v>43909</v>
-      </c>
-      <c r="C22" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="91">
-        <v>2155</v>
-      </c>
-      <c r="E22" s="91">
-        <v>1692</v>
-      </c>
-      <c r="F22" s="91">
-        <v>573</v>
-      </c>
-      <c r="G22" s="91">
-        <v>134</v>
-      </c>
-      <c r="H22" s="91">
-        <v>80</v>
-      </c>
-      <c r="I22" s="91">
-        <v>432</v>
-      </c>
-      <c r="J22" s="91">
-        <v>682</v>
-      </c>
-      <c r="K22" s="91">
-        <v>98</v>
-      </c>
-      <c r="L22" s="91">
-        <v>669</v>
-      </c>
-      <c r="M22" s="91">
-        <v>3033</v>
-      </c>
-      <c r="N22" s="91">
-        <v>637</v>
-      </c>
-      <c r="O22" s="91">
-        <v>99</v>
-      </c>
-      <c r="P22" s="91">
-        <v>275</v>
-      </c>
-      <c r="Q22" s="91">
-        <v>140</v>
-      </c>
-      <c r="R22" s="91">
-        <v>202</v>
-      </c>
-      <c r="S22" s="91">
-        <v>98</v>
-      </c>
-      <c r="T22" s="92">
-        <v>10999</v>
-      </c>
-      <c r="U22" s="38">
-        <f>IF(ISNUMBER(T21),T22-T21,"")</f>
-        <v>2801</v>
-      </c>
-      <c r="V22" s="39">
-        <f>IF(ISNUMBER(T21),
-((T22-T21)/T21)/(B22-B21),
-"")</f>
-        <v>0.34166869968284946</v>
-      </c>
-      <c r="W22" s="88">
-        <f>guide_start*EXP(Table5[[#This Row],['#]]*(LN(2)/guide_doubling))</f>
-        <v>5248.2011333370947</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="69">
-        <f>A24-1</f>
-        <v>-1</v>
-      </c>
-      <c r="B23" s="37">
-        <v>43910</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="48">
-        <v>2746</v>
-      </c>
-      <c r="E23" s="48">
-        <v>2401</v>
-      </c>
-      <c r="F23" s="48">
-        <v>731</v>
-      </c>
-      <c r="G23" s="48">
-        <v>192</v>
-      </c>
-      <c r="H23" s="48">
-        <v>121</v>
-      </c>
-      <c r="I23" s="48">
-        <v>586</v>
-      </c>
-      <c r="J23" s="48">
-        <v>813</v>
-      </c>
-      <c r="K23" s="48">
-        <v>131</v>
-      </c>
-      <c r="L23" s="48">
-        <v>803</v>
-      </c>
-      <c r="M23" s="48">
-        <v>3497</v>
-      </c>
-      <c r="N23" s="48">
-        <v>801</v>
-      </c>
-      <c r="O23" s="48">
-        <v>146</v>
-      </c>
-      <c r="P23" s="48">
-        <v>394</v>
-      </c>
-      <c r="Q23" s="48">
-        <v>180</v>
-      </c>
-      <c r="R23" s="48">
-        <v>266</v>
-      </c>
-      <c r="S23" s="48">
-        <v>149</v>
-      </c>
-      <c r="T23" s="48">
-        <v>13957</v>
-      </c>
-      <c r="U23" s="38">
-        <f>IF(ISNUMBER(T22),T23-T22,"")</f>
-        <v>2958</v>
-      </c>
-      <c r="V23" s="39">
-        <f>IF(ISNUMBER(T22),
-((T23-T22)/T22)/(B23-B22),
-"")</f>
-        <v>0.26893353941267389</v>
-      </c>
-      <c r="W23" s="88">
-        <f>guide_start*EXP(Table5[[#This Row],['#]]*(LN(2)/guide_doubling))</f>
-        <v>6612.3190819735355</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
-      <c r="A24" s="69">
-        <v>0</v>
-      </c>
-      <c r="B24" s="37">
-        <v>43911</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="66">
-        <v>3668</v>
-      </c>
-      <c r="E24" s="66">
-        <v>2960</v>
-      </c>
-      <c r="F24" s="66">
-        <v>866</v>
-      </c>
-      <c r="G24" s="66">
-        <v>254</v>
-      </c>
-      <c r="H24" s="66">
-        <v>142</v>
-      </c>
-      <c r="I24" s="66">
-        <v>587</v>
-      </c>
-      <c r="J24" s="66">
-        <v>1080</v>
-      </c>
-      <c r="K24" s="66">
-        <v>165</v>
-      </c>
-      <c r="L24" s="66">
-        <v>1023</v>
-      </c>
-      <c r="M24" s="66">
-        <v>3542</v>
-      </c>
-      <c r="N24" s="66">
-        <v>938</v>
-      </c>
-      <c r="O24" s="66">
-        <v>187</v>
-      </c>
-      <c r="P24" s="66">
-        <v>567</v>
-      </c>
-      <c r="Q24" s="66">
-        <v>188</v>
-      </c>
-      <c r="R24" s="66">
-        <v>308</v>
-      </c>
-      <c r="S24" s="66">
-        <v>187</v>
-      </c>
-      <c r="T24" s="66">
-        <v>16662</v>
-      </c>
-      <c r="U24" s="38">
-        <f>IF(ISNUMBER(T23),T24-T23,"")</f>
-        <v>2705</v>
-      </c>
-      <c r="V24" s="39">
-        <f>IF(ISNUMBER(T23),
-((T24-T23)/T23)/(B24-B23),
-"")</f>
-        <v>0.19380955792792148</v>
-      </c>
-      <c r="W24" s="88">
-        <f>guide_start*EXP(Table5[[#This Row],['#]]*(LN(2)/guide_doubling))</f>
-        <v>8331</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35575D0-0A0E-6E43-9D76-74E38D2BC332}">
   <dimension ref="A1:V24"/>
